--- a/BWI/bestwine_output/bestwine_Cyprus.xlsx
+++ b/BWI/bestwine_output/bestwine_Cyprus.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA146"/>
+  <dimension ref="A1:AA148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16555,6 +16555,224 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Photos Photiades Group Limited</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Photos Photiades Group Limited</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>62654</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Nicosia</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Nicosia</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>8 Stassinos Avenue</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>https://photiadesgroup.com</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr"/>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>info@photiadesgroup.com</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>+357 22 452000</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>HE44933</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/photos-photiades-group/</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/photosphotiadesgroup/</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/photiadesgroup/</t>
+        </is>
+      </c>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PhotiadesGroup</t>
+        </is>
+      </c>
+      <c r="W147" s="2" t="inlineStr">
+        <is>
+          <t>Eva Christodoulou</t>
+        </is>
+      </c>
+      <c r="X147" s="2" t="inlineStr">
+        <is>
+          <t>International Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y147" s="2" t="inlineStr"/>
+      <c r="Z147" s="2" t="inlineStr"/>
+      <c r="AA147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eva-christodoulou/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Photos Photiades Group Limited</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Photos Photiades Group Limited</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>62654</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Nicosia</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Nicosia</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>8 Stassinos Avenue</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>https://photiadesgroup.com</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>info@photiadesgroup.com</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>+357 22 452000</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>HE44933</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/photos-photiades-group/</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/photosphotiadesgroup/</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/photiadesgroup/</t>
+        </is>
+      </c>
+      <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PhotiadesGroup</t>
+        </is>
+      </c>
+      <c r="W148" s="2" t="inlineStr">
+        <is>
+          <t>Chrystalla Demetriou</t>
+        </is>
+      </c>
+      <c r="X148" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing &amp; Exports Officer</t>
+        </is>
+      </c>
+      <c r="Y148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="AA148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chrystalla-demetriou-0b70681b4/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Cyprus.xlsx
+++ b/BWI/bestwine_output/bestwine_Cyprus.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA148"/>
+  <dimension ref="A1:AA154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16773,6 +16773,644 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Volta Wine Bar</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Volta Wine Bar</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>122615</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Limassol</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Limassol</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Attikis 1</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>3031</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>https://voltawinebar.com</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>voltawinebar@gmail.com</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr"/>
+      <c r="P149" s="2" t="inlineStr"/>
+      <c r="Q149" s="2" t="inlineStr"/>
+      <c r="R149" s="2" t="inlineStr"/>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/voltawinebar/</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/voltawinebar/</t>
+        </is>
+      </c>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@VoltaWineBar</t>
+        </is>
+      </c>
+      <c r="W149" s="2" t="inlineStr"/>
+      <c r="X149" s="2" t="inlineStr"/>
+      <c r="Y149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Xinaris &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Xinaris &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>22325</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Lefkoşa</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Lefkoşa kazası</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Bella Pais 19</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xinaris.net</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>info@xinaris.net</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>+357 22 345070</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>HE21416</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/asxinaris/</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/asxinaris/</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.s.xinaris/</t>
+        </is>
+      </c>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@a.s.xinarissonsltd1388</t>
+        </is>
+      </c>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>Stefanos Xinaris</t>
+        </is>
+      </c>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stefanos-xinaris-966081182</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Xinaris &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Xinaris &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>22325</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Lefkoşa</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Lefkoşa kazası</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Bella Pais 19</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xinaris.net</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>info@xinaris.net</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>+357 22 345070</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>HE21416</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/asxinaris/</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/asxinaris/</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.s.xinaris/</t>
+        </is>
+      </c>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@a.s.xinarissonsltd1388</t>
+        </is>
+      </c>
+      <c r="W151" s="2" t="inlineStr">
+        <is>
+          <t>George Voutouris</t>
+        </is>
+      </c>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/george-voutouris/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Xinaris &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Xinaris &amp; Sons Limited</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>22325</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Lefkoşa</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Lefkoşa kazası</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Bella Pais 19</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.xinaris.net</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>info@xinaris.net</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>+357 22 345070</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>HE21416</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/asxinaris/</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/asxinaris/</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.s.xinaris/</t>
+        </is>
+      </c>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@a.s.xinarissonsltd1388</t>
+        </is>
+      </c>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>Panayiotis Xinaris</t>
+        </is>
+      </c>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/panayiotis-xinaris-8a49a28b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Photos Photiades Group Limited</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Photos Photiades Group Limited</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>62654</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Nicosia</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Nicosia</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>8 Stassinos Avenue</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://photiadesgroup.com</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr"/>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>info@photiadesgroup.com</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>+357 22 452000</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>HE44933</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/photos-photiades-group/</t>
+        </is>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/photosphotiadesgroup/</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/photiadesgroup/</t>
+        </is>
+      </c>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PhotiadesGroup</t>
+        </is>
+      </c>
+      <c r="W153" s="2" t="inlineStr">
+        <is>
+          <t>Eva Christodoulou</t>
+        </is>
+      </c>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t>International Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eva-christodoulou/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Photos Photiades Group Limited</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Photos Photiades Group Limited</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>62654</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Nicosia</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Nicosia</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>8 Stassinos Avenue</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://photiadesgroup.com</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>info@photiadesgroup.com</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>+357 22 452000</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>HE44933</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/photos-photiades-group/</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/photosphotiadesgroup/</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/photiadesgroup/</t>
+        </is>
+      </c>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PhotiadesGroup</t>
+        </is>
+      </c>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
+          <t>Chrystalla Demetriou</t>
+        </is>
+      </c>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing &amp; Exports Officer</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chrystalla-demetriou-0b70681b4/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
